--- a/Deliverable/Main_Board/BOM/LCSC_BOM.xlsx
+++ b/Deliverable/Main_Board/BOM/LCSC_BOM.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24931"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GrantKros-CoopMonitor\Deliverable\Main_Board\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GrantKros-CoopMonitor\Deliverable\Main_Board\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF6BB9D2-177C-4A07-87DF-C6C2B0C1280F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10725" yWindow="3165" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-10725" yWindow="3165" windowWidth="21600" windowHeight="11385"/>
   </bookViews>
   <sheets>
     <sheet name="LCSC_BOM" sheetId="1" r:id="rId1"/>
@@ -18,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">LCSC_BOM!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="349">
   <si>
     <t>Bill of Material (BOM) for Grant</t>
   </si>
@@ -688,9 +687,6 @@
     <t>RES SMD 0 OHM JUMPER 1/16W 0402</t>
   </si>
   <si>
-    <t>R18, R19, RF22, RF23</t>
-  </si>
-  <si>
     <t>RC0402JR-070RL</t>
   </si>
   <si>
@@ -1080,18 +1076,42 @@
   </si>
   <si>
     <t>C35445</t>
+  </si>
+  <si>
+    <t>Donot Mount R18</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>R18</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>, R19, RF22, RF23</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000_);[Red]\(&quot;$&quot;#,##0.0000\)"/>
-    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.0000"/>
-    <numFmt numFmtId="168" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1252,6 +1272,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <strike/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -2092,13 +2119,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2122,10 +2149,10 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="19" fillId="4" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="19" fillId="4" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="19" fillId="4" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="4" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2224,6 +2251,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2260,64 +2314,37 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="27" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="27" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2595,7 +2622,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2629,33 +2656,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" s="1" customFormat="1" ht="15.75">
-      <c r="A1" s="140" t="s">
+      <c r="A1" s="149" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="141"/>
-      <c r="C1" s="141"/>
-      <c r="D1" s="141"/>
-      <c r="E1" s="141"/>
-      <c r="F1" s="141"/>
-      <c r="G1" s="141"/>
-      <c r="H1" s="141"/>
-      <c r="I1" s="141"/>
-      <c r="J1" s="141"/>
-      <c r="K1" s="141"/>
-      <c r="L1" s="141"/>
-      <c r="M1" s="141"/>
-      <c r="N1" s="141"/>
-      <c r="O1" s="141"/>
-      <c r="P1" s="141"/>
-      <c r="Q1" s="141"/>
-      <c r="R1" s="141"/>
-      <c r="S1" s="141"/>
-      <c r="T1" s="141"/>
-      <c r="U1" s="141"/>
-      <c r="V1" s="141"/>
-      <c r="W1" s="141"/>
-      <c r="X1" s="141"/>
-      <c r="Y1" s="142"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="150"/>
+      <c r="G1" s="150"/>
+      <c r="H1" s="150"/>
+      <c r="I1" s="150"/>
+      <c r="J1" s="150"/>
+      <c r="K1" s="150"/>
+      <c r="L1" s="150"/>
+      <c r="M1" s="150"/>
+      <c r="N1" s="150"/>
+      <c r="O1" s="150"/>
+      <c r="P1" s="150"/>
+      <c r="Q1" s="150"/>
+      <c r="R1" s="150"/>
+      <c r="S1" s="150"/>
+      <c r="T1" s="150"/>
+      <c r="U1" s="150"/>
+      <c r="V1" s="150"/>
+      <c r="W1" s="150"/>
+      <c r="X1" s="150"/>
+      <c r="Y1" s="151"/>
     </row>
     <row r="2" spans="1:26" s="2" customFormat="1" ht="15.75">
       <c r="A2" s="6" t="s">
@@ -2739,13 +2766,13 @@
       <c r="A3" s="7">
         <v>1</v>
       </c>
-      <c r="B3" s="145" t="s">
+      <c r="B3" s="154" t="s">
         <v>24</v>
       </c>
       <c r="C3" s="109" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="153" t="s">
+      <c r="D3" s="161" t="s">
         <v>26</v>
       </c>
       <c r="E3" s="110" t="s">
@@ -2820,11 +2847,11 @@
       <c r="A4" s="7">
         <v>2</v>
       </c>
-      <c r="B4" s="146"/>
+      <c r="B4" s="155"/>
       <c r="C4" s="111" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="152" t="s">
+      <c r="D4" s="145" t="s">
         <v>35</v>
       </c>
       <c r="E4" s="112" t="s">
@@ -2899,12 +2926,12 @@
       <c r="A5" s="7">
         <v>3</v>
       </c>
-      <c r="B5" s="146"/>
+      <c r="B5" s="155"/>
       <c r="C5" s="111" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="154" t="s">
-        <v>337</v>
+      <c r="D5" s="162" t="s">
+        <v>336</v>
       </c>
       <c r="E5" s="112" t="s">
         <v>41</v>
@@ -2973,18 +3000,18 @@
         <v>24.5</v>
       </c>
       <c r="Y5" s="83" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="15.75" thickBot="1">
       <c r="A6" s="7">
         <v>4</v>
       </c>
-      <c r="B6" s="146"/>
+      <c r="B6" s="155"/>
       <c r="C6" s="111" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="152" t="s">
+      <c r="D6" s="145" t="s">
         <v>48</v>
       </c>
       <c r="E6" s="112" t="s">
@@ -3059,11 +3086,11 @@
       <c r="A7" s="7">
         <v>5</v>
       </c>
-      <c r="B7" s="146"/>
+      <c r="B7" s="155"/>
       <c r="C7" s="111" t="s">
         <v>54</v>
       </c>
-      <c r="D7" s="152" t="s">
+      <c r="D7" s="145" t="s">
         <v>55</v>
       </c>
       <c r="E7" s="112" t="s">
@@ -3138,11 +3165,11 @@
       <c r="A8" s="7">
         <v>6</v>
       </c>
-      <c r="B8" s="146"/>
+      <c r="B8" s="155"/>
       <c r="C8" s="111" t="s">
         <v>60</v>
       </c>
-      <c r="D8" s="152" t="s">
+      <c r="D8" s="145" t="s">
         <v>61</v>
       </c>
       <c r="E8" s="112" t="s">
@@ -3217,11 +3244,11 @@
       <c r="A9" s="7">
         <v>7</v>
       </c>
-      <c r="B9" s="146"/>
+      <c r="B9" s="155"/>
       <c r="C9" s="111" t="s">
         <v>67</v>
       </c>
-      <c r="D9" s="152" t="s">
+      <c r="D9" s="145" t="s">
         <v>68</v>
       </c>
       <c r="E9" s="112" t="s">
@@ -3296,11 +3323,11 @@
       <c r="A10" s="7">
         <v>8</v>
       </c>
-      <c r="B10" s="146"/>
+      <c r="B10" s="155"/>
       <c r="C10" s="111" t="s">
         <v>74</v>
       </c>
-      <c r="D10" s="152" t="s">
+      <c r="D10" s="145" t="s">
         <v>75</v>
       </c>
       <c r="E10" s="112" t="s">
@@ -3375,11 +3402,11 @@
       <c r="A11" s="7">
         <v>9</v>
       </c>
-      <c r="B11" s="146"/>
+      <c r="B11" s="155"/>
       <c r="C11" s="111" t="s">
         <v>81</v>
       </c>
-      <c r="D11" s="152" t="s">
+      <c r="D11" s="145" t="s">
         <v>82</v>
       </c>
       <c r="E11" s="112" t="s">
@@ -3454,11 +3481,11 @@
       <c r="A12" s="7">
         <v>10</v>
       </c>
-      <c r="B12" s="146"/>
+      <c r="B12" s="155"/>
       <c r="C12" s="115" t="s">
         <v>88</v>
       </c>
-      <c r="D12" s="155" t="s">
+      <c r="D12" s="163" t="s">
         <v>89</v>
       </c>
       <c r="E12" s="116" t="s">
@@ -3535,12 +3562,12 @@
       <c r="A13" s="7">
         <v>12</v>
       </c>
-      <c r="B13" s="146"/>
+      <c r="B13" s="155"/>
       <c r="C13" s="111" t="s">
         <v>96</v>
       </c>
-      <c r="D13" s="152" t="s">
-        <v>339</v>
+      <c r="D13" s="145" t="s">
+        <v>338</v>
       </c>
       <c r="E13" s="112" t="s">
         <v>62</v>
@@ -3614,12 +3641,12 @@
       <c r="A14" s="7">
         <v>13</v>
       </c>
-      <c r="B14" s="146"/>
+      <c r="B14" s="155"/>
       <c r="C14" s="111" t="s">
         <v>101</v>
       </c>
-      <c r="D14" s="152" t="s">
-        <v>340</v>
+      <c r="D14" s="145" t="s">
+        <v>339</v>
       </c>
       <c r="E14" s="112" t="s">
         <v>41</v>
@@ -3693,11 +3720,11 @@
       <c r="A15" s="7">
         <v>14</v>
       </c>
-      <c r="B15" s="146"/>
+      <c r="B15" s="155"/>
       <c r="C15" s="111" t="s">
         <v>106</v>
       </c>
-      <c r="D15" s="152" t="s">
+      <c r="D15" s="145" t="s">
         <v>107</v>
       </c>
       <c r="E15" s="112" t="s">
@@ -3772,11 +3799,11 @@
       <c r="A16" s="7">
         <v>15</v>
       </c>
-      <c r="B16" s="147"/>
+      <c r="B16" s="156"/>
       <c r="C16" s="118" t="s">
         <v>112</v>
       </c>
-      <c r="D16" s="156" t="s">
+      <c r="D16" s="164" t="s">
         <v>113</v>
       </c>
       <c r="E16" s="119" t="s">
@@ -3849,13 +3876,13 @@
     </row>
     <row r="17" spans="1:25">
       <c r="A17" s="7"/>
-      <c r="B17" s="148" t="s">
+      <c r="B17" s="157" t="s">
         <v>117</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="D17" s="157" t="s">
+      <c r="D17" s="165" t="s">
         <v>119</v>
       </c>
       <c r="E17" s="110" t="s">
@@ -3930,11 +3957,11 @@
       <c r="A18" s="7">
         <v>16</v>
       </c>
-      <c r="B18" s="149"/>
+      <c r="B18" s="158"/>
       <c r="C18" s="120" t="s">
         <v>125</v>
       </c>
-      <c r="D18" s="158" t="s">
+      <c r="D18" s="166" t="s">
         <v>126</v>
       </c>
       <c r="E18" s="121" t="s">
@@ -4017,8 +4044,8 @@
       <c r="C19" s="123" t="s">
         <v>134</v>
       </c>
-      <c r="D19" s="159" t="s">
-        <v>341</v>
+      <c r="D19" s="167" t="s">
+        <v>340</v>
       </c>
       <c r="E19" s="124" t="s">
         <v>135</v>
@@ -4092,13 +4119,13 @@
       <c r="A20" s="7">
         <v>18</v>
       </c>
-      <c r="B20" s="150" t="s">
+      <c r="B20" s="159" t="s">
         <v>139</v>
       </c>
       <c r="C20" s="125" t="s">
         <v>140</v>
       </c>
-      <c r="D20" s="160" t="s">
+      <c r="D20" s="168" t="s">
         <v>141</v>
       </c>
       <c r="E20" s="126" t="s">
@@ -4173,11 +4200,11 @@
       <c r="A21" s="7">
         <v>20</v>
       </c>
-      <c r="B21" s="146"/>
+      <c r="B21" s="155"/>
       <c r="C21" s="111" t="s">
         <v>146</v>
       </c>
-      <c r="D21" s="152" t="s">
+      <c r="D21" s="145" t="s">
         <v>147</v>
       </c>
       <c r="E21" s="112" t="s">
@@ -4252,11 +4279,11 @@
       <c r="A22" s="7">
         <v>21</v>
       </c>
-      <c r="B22" s="146"/>
+      <c r="B22" s="155"/>
       <c r="C22" s="111" t="s">
         <v>151</v>
       </c>
-      <c r="D22" s="152" t="s">
+      <c r="D22" s="145" t="s">
         <v>152</v>
       </c>
       <c r="E22" s="112" t="s">
@@ -4331,13 +4358,13 @@
       <c r="A23" s="7">
         <v>23</v>
       </c>
-      <c r="B23" s="145" t="s">
+      <c r="B23" s="154" t="s">
         <v>156</v>
       </c>
       <c r="C23" s="109" t="s">
         <v>157</v>
       </c>
-      <c r="D23" s="153" t="s">
+      <c r="D23" s="161" t="s">
         <v>158</v>
       </c>
       <c r="E23" s="110" t="s">
@@ -4412,11 +4439,11 @@
       <c r="A24" s="7">
         <v>24</v>
       </c>
-      <c r="B24" s="151"/>
+      <c r="B24" s="160"/>
       <c r="C24" s="120" t="s">
         <v>162</v>
       </c>
-      <c r="D24" s="158" t="s">
+      <c r="D24" s="166" t="s">
         <v>163</v>
       </c>
       <c r="E24" s="121" t="s">
@@ -4497,7 +4524,7 @@
       <c r="C25" s="128" t="s">
         <v>168</v>
       </c>
-      <c r="D25" s="161" t="s">
+      <c r="D25" s="169" t="s">
         <v>169</v>
       </c>
       <c r="E25" s="129" t="s">
@@ -4578,7 +4605,7 @@
       <c r="C26" s="130" t="s">
         <v>174</v>
       </c>
-      <c r="D26" s="162" t="s">
+      <c r="D26" s="170" t="s">
         <v>175</v>
       </c>
       <c r="E26" s="131" t="s">
@@ -4653,13 +4680,13 @@
       <c r="A27" s="7">
         <v>27</v>
       </c>
-      <c r="B27" s="145" t="s">
+      <c r="B27" s="154" t="s">
         <v>179</v>
       </c>
       <c r="C27" s="109" t="s">
         <v>180</v>
       </c>
-      <c r="D27" s="153" t="s">
+      <c r="D27" s="161" t="s">
         <v>181</v>
       </c>
       <c r="E27" s="110" t="s">
@@ -4734,11 +4761,11 @@
       <c r="A28" s="7">
         <v>28</v>
       </c>
-      <c r="B28" s="146"/>
+      <c r="B28" s="155"/>
       <c r="C28" s="111" t="s">
         <v>187</v>
       </c>
-      <c r="D28" s="152" t="s">
+      <c r="D28" s="145" t="s">
         <v>188</v>
       </c>
       <c r="E28" s="112" t="s">
@@ -4813,12 +4840,12 @@
       <c r="A29" s="7">
         <v>29</v>
       </c>
-      <c r="B29" s="146"/>
+      <c r="B29" s="155"/>
       <c r="C29" s="111" t="s">
         <v>195</v>
       </c>
-      <c r="D29" s="152" t="s">
-        <v>342</v>
+      <c r="D29" s="145" t="s">
+        <v>341</v>
       </c>
       <c r="E29" s="112" t="s">
         <v>182</v>
@@ -4892,12 +4919,12 @@
       <c r="A30" s="7">
         <v>33</v>
       </c>
-      <c r="B30" s="146"/>
+      <c r="B30" s="155"/>
       <c r="C30" s="111" t="s">
         <v>199</v>
       </c>
-      <c r="D30" s="152" t="s">
-        <v>343</v>
+      <c r="D30" s="145" t="s">
+        <v>342</v>
       </c>
       <c r="E30" s="112" t="s">
         <v>182</v>
@@ -4971,11 +4998,11 @@
       <c r="A31" s="7">
         <v>34</v>
       </c>
-      <c r="B31" s="146"/>
+      <c r="B31" s="155"/>
       <c r="C31" s="111" t="s">
         <v>205</v>
       </c>
-      <c r="D31" s="152" t="s">
+      <c r="D31" s="145" t="s">
         <v>206</v>
       </c>
       <c r="E31" s="112" t="s">
@@ -5050,11 +5077,11 @@
       <c r="A32" s="7">
         <v>35</v>
       </c>
-      <c r="B32" s="146"/>
+      <c r="B32" s="155"/>
       <c r="C32" s="111" t="s">
         <v>210</v>
       </c>
-      <c r="D32" s="152" t="s">
+      <c r="D32" s="145" t="s">
         <v>211</v>
       </c>
       <c r="E32" s="112" t="s">
@@ -5129,45 +5156,45 @@
       <c r="A33" s="7">
         <v>36</v>
       </c>
-      <c r="B33" s="146"/>
+      <c r="B33" s="155"/>
       <c r="C33" s="111" t="s">
         <v>216</v>
       </c>
-      <c r="D33" s="152" t="s">
-        <v>217</v>
+      <c r="D33" s="145" t="s">
+        <v>348</v>
       </c>
       <c r="E33" s="112" t="s">
         <v>182</v>
       </c>
       <c r="F33" s="112" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G33" s="10" t="s">
         <v>43</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I33" s="28" t="s">
         <v>31</v>
       </c>
       <c r="J33" s="112" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K33" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L33" s="10">
         <f t="shared" si="12"/>
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="M33" s="10">
         <f t="shared" si="13"/>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="N33" s="10">
         <f t="shared" si="14"/>
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="O33" s="29">
         <v>100</v>
@@ -5202,36 +5229,38 @@
         <f t="shared" si="17"/>
         <v>0.35</v>
       </c>
-      <c r="Y33" s="82"/>
+      <c r="Y33" s="148" t="s">
+        <v>347</v>
+      </c>
     </row>
     <row r="34" spans="1:25" ht="15.75" thickBot="1">
       <c r="A34" s="7">
         <v>39</v>
       </c>
-      <c r="B34" s="146"/>
+      <c r="B34" s="155"/>
       <c r="C34" s="111" t="s">
+        <v>220</v>
+      </c>
+      <c r="D34" s="171" t="s">
         <v>221</v>
-      </c>
-      <c r="D34" s="163" t="s">
-        <v>222</v>
       </c>
       <c r="E34" s="112" t="s">
         <v>182</v>
       </c>
       <c r="F34" s="112" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G34" s="10" t="s">
         <v>43</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I34" s="28" t="s">
         <v>31</v>
       </c>
       <c r="J34" s="112" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K34" s="10">
         <v>3</v>
@@ -5287,30 +5316,30 @@
       <c r="A35" s="7">
         <v>40</v>
       </c>
-      <c r="B35" s="146"/>
+      <c r="B35" s="155"/>
       <c r="C35" s="111" t="s">
-        <v>226</v>
-      </c>
-      <c r="D35" s="152" t="s">
-        <v>344</v>
+        <v>225</v>
+      </c>
+      <c r="D35" s="145" t="s">
+        <v>343</v>
       </c>
       <c r="E35" s="112" t="s">
         <v>182</v>
       </c>
       <c r="F35" s="113" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G35" s="10" t="s">
         <v>29</v>
       </c>
       <c r="H35" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="I35" s="48" t="s">
         <v>228</v>
       </c>
-      <c r="I35" s="48" t="s">
+      <c r="J35" s="112" t="s">
         <v>229</v>
-      </c>
-      <c r="J35" s="112" t="s">
-        <v>230</v>
       </c>
       <c r="K35" s="10">
         <v>2</v>
@@ -5366,30 +5395,30 @@
       <c r="A36" s="7">
         <v>43</v>
       </c>
-      <c r="B36" s="146"/>
+      <c r="B36" s="155"/>
       <c r="C36" s="111" t="s">
+        <v>230</v>
+      </c>
+      <c r="D36" s="145" t="s">
         <v>231</v>
-      </c>
-      <c r="D36" s="152" t="s">
-        <v>232</v>
       </c>
       <c r="E36" s="112" t="s">
         <v>182</v>
       </c>
       <c r="F36" s="112" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G36" s="10" t="s">
         <v>43</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I36" s="28" t="s">
         <v>31</v>
       </c>
       <c r="J36" s="112" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K36" s="10">
         <v>1</v>
@@ -5445,30 +5474,30 @@
       <c r="A37" s="7">
         <v>44</v>
       </c>
-      <c r="B37" s="146"/>
+      <c r="B37" s="155"/>
       <c r="C37" s="111" t="s">
+        <v>235</v>
+      </c>
+      <c r="D37" s="145" t="s">
         <v>236</v>
-      </c>
-      <c r="D37" s="152" t="s">
-        <v>237</v>
       </c>
       <c r="E37" s="112" t="s">
         <v>182</v>
       </c>
       <c r="F37" s="112" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G37" s="10" t="s">
         <v>43</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I37" s="28" t="s">
         <v>31</v>
       </c>
       <c r="J37" s="112" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K37" s="10">
         <v>1</v>
@@ -5524,26 +5553,26 @@
       <c r="A38" s="7">
         <v>48</v>
       </c>
-      <c r="B38" s="145" t="s">
+      <c r="B38" s="154" t="s">
+        <v>240</v>
+      </c>
+      <c r="C38" s="109" t="s">
         <v>241</v>
       </c>
-      <c r="C38" s="109" t="s">
+      <c r="D38" s="161" t="s">
         <v>242</v>
-      </c>
-      <c r="D38" s="153" t="s">
-        <v>243</v>
       </c>
       <c r="E38" s="132" t="s">
         <v>155</v>
       </c>
       <c r="F38" s="110" t="s">
+        <v>243</v>
+      </c>
+      <c r="G38" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="G38" s="9" t="s">
+      <c r="H38" s="9" t="s">
         <v>245</v>
-      </c>
-      <c r="H38" s="9" t="s">
-        <v>246</v>
       </c>
       <c r="I38" s="26" t="s">
         <v>31</v>
@@ -5605,21 +5634,21 @@
       <c r="A39" s="7">
         <v>52</v>
       </c>
-      <c r="B39" s="146"/>
+      <c r="B39" s="155"/>
       <c r="C39" s="115" t="s">
+        <v>247</v>
+      </c>
+      <c r="D39" s="163" t="s">
         <v>248</v>
       </c>
-      <c r="D39" s="155" t="s">
+      <c r="E39" s="116" t="s">
         <v>249</v>
       </c>
-      <c r="E39" s="116" t="s">
+      <c r="F39" s="116" t="s">
         <v>250</v>
       </c>
-      <c r="F39" s="116" t="s">
+      <c r="G39" s="12" t="s">
         <v>251</v>
-      </c>
-      <c r="G39" s="12" t="s">
-        <v>252</v>
       </c>
       <c r="H39" s="12"/>
       <c r="I39" s="50" t="s">
@@ -5663,31 +5692,31 @@
         <v>0</v>
       </c>
       <c r="Y39" s="84" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="40" spans="1:25">
       <c r="A40" s="7">
         <v>53</v>
       </c>
-      <c r="B40" s="146"/>
+      <c r="B40" s="155"/>
       <c r="C40" s="111" t="s">
+        <v>253</v>
+      </c>
+      <c r="D40" s="145" t="s">
         <v>254</v>
       </c>
-      <c r="D40" s="152" t="s">
+      <c r="E40" s="112" t="s">
         <v>255</v>
       </c>
-      <c r="E40" s="112" t="s">
+      <c r="F40" s="112" t="s">
         <v>256</v>
       </c>
-      <c r="F40" s="112" t="s">
+      <c r="G40" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="G40" s="10" t="s">
+      <c r="H40" s="10" t="s">
         <v>258</v>
-      </c>
-      <c r="H40" s="10" t="s">
-        <v>259</v>
       </c>
       <c r="I40" s="28" t="s">
         <v>31</v>
@@ -5749,21 +5778,21 @@
       <c r="A41" s="7">
         <v>54</v>
       </c>
-      <c r="B41" s="146"/>
+      <c r="B41" s="155"/>
       <c r="C41" s="115" t="s">
+        <v>259</v>
+      </c>
+      <c r="D41" s="163" t="s">
         <v>260</v>
       </c>
-      <c r="D41" s="155" t="s">
+      <c r="E41" s="116" t="s">
         <v>261</v>
       </c>
-      <c r="E41" s="116" t="s">
+      <c r="F41" s="116" t="s">
         <v>262</v>
       </c>
-      <c r="F41" s="116" t="s">
-        <v>263</v>
-      </c>
       <c r="G41" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H41" s="12"/>
       <c r="I41" s="50" t="s">
@@ -5797,7 +5826,7 @@
         <v>120</v>
       </c>
       <c r="R41" s="80" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="S41" s="59">
         <v>1.1499999999999999</v>
@@ -5826,24 +5855,24 @@
       <c r="A42" s="7">
         <v>55</v>
       </c>
-      <c r="B42" s="146"/>
+      <c r="B42" s="155"/>
       <c r="C42" s="111" t="s">
+        <v>263</v>
+      </c>
+      <c r="D42" s="145" t="s">
         <v>264</v>
       </c>
-      <c r="D42" s="152" t="s">
+      <c r="E42" s="112" t="s">
+        <v>255</v>
+      </c>
+      <c r="F42" s="112" t="s">
         <v>265</v>
       </c>
-      <c r="E42" s="112" t="s">
-        <v>256</v>
-      </c>
-      <c r="F42" s="112" t="s">
+      <c r="G42" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="H42" s="10" t="s">
         <v>266</v>
-      </c>
-      <c r="G42" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="H42" s="10" t="s">
-        <v>267</v>
       </c>
       <c r="I42" s="28" t="s">
         <v>31</v>
@@ -5905,24 +5934,24 @@
       <c r="A43" s="7">
         <v>57</v>
       </c>
-      <c r="B43" s="151"/>
+      <c r="B43" s="160"/>
       <c r="C43" s="120" t="s">
+        <v>267</v>
+      </c>
+      <c r="D43" s="166" t="s">
         <v>268</v>
       </c>
-      <c r="D43" s="158" t="s">
+      <c r="E43" s="121" t="s">
         <v>269</v>
       </c>
-      <c r="E43" s="121" t="s">
+      <c r="F43" s="121" t="s">
         <v>270</v>
       </c>
-      <c r="F43" s="121" t="s">
+      <c r="G43" s="17" t="s">
         <v>271</v>
       </c>
-      <c r="G43" s="17" t="s">
+      <c r="H43" s="17" t="s">
         <v>272</v>
-      </c>
-      <c r="H43" s="17" t="s">
-        <v>273</v>
       </c>
       <c r="I43" s="42" t="s">
         <v>31</v>
@@ -5984,31 +6013,31 @@
       <c r="A44" s="7">
         <v>58</v>
       </c>
-      <c r="B44" s="145" t="s">
+      <c r="B44" s="154" t="s">
+        <v>273</v>
+      </c>
+      <c r="C44" s="133" t="s">
+        <v>345</v>
+      </c>
+      <c r="D44" s="145" t="s">
         <v>274</v>
       </c>
-      <c r="C44" s="133" t="s">
+      <c r="E44" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="F44" s="144" t="s">
         <v>346</v>
       </c>
-      <c r="D44" s="152" t="s">
-        <v>275</v>
-      </c>
-      <c r="E44" s="169" t="s">
-        <v>27</v>
-      </c>
-      <c r="F44" s="168" t="s">
-        <v>347</v>
-      </c>
       <c r="G44" s="10" t="s">
-        <v>306</v>
-      </c>
-      <c r="H44" s="170" t="s">
-        <v>347</v>
-      </c>
-      <c r="I44" s="164" t="s">
+        <v>305</v>
+      </c>
+      <c r="H44" s="146" t="s">
+        <v>346</v>
+      </c>
+      <c r="I44" s="140" t="s">
         <v>31</v>
       </c>
-      <c r="J44" s="164" t="s">
+      <c r="J44" s="140" t="s">
         <v>124</v>
       </c>
       <c r="K44" s="24">
@@ -6026,63 +6055,63 @@
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
-      <c r="O44" s="165">
+      <c r="O44" s="141">
         <v>10</v>
       </c>
-      <c r="P44" s="165">
+      <c r="P44" s="141">
         <v>60</v>
       </c>
-      <c r="Q44" s="165">
+      <c r="Q44" s="141">
         <v>110</v>
       </c>
-      <c r="R44" s="171" t="s">
+      <c r="R44" s="147" t="s">
         <v>33</v>
       </c>
-      <c r="S44" s="166">
+      <c r="S44" s="142">
         <v>8.1299999999999997E-2</v>
       </c>
-      <c r="T44" s="166">
+      <c r="T44" s="142">
         <f t="shared" si="15"/>
         <v>0.81299999999999994</v>
       </c>
-      <c r="U44" s="166">
+      <c r="U44" s="142">
         <v>8.1299999999999997E-2</v>
       </c>
-      <c r="V44" s="166">
+      <c r="V44" s="142">
         <f t="shared" si="16"/>
         <v>4.8780000000000001</v>
       </c>
-      <c r="W44" s="166">
+      <c r="W44" s="142">
         <v>6.7199999999999996E-2</v>
       </c>
-      <c r="X44" s="166">
+      <c r="X44" s="142">
         <f t="shared" si="17"/>
         <v>7.3919999999999995</v>
       </c>
-      <c r="Y44" s="167"/>
+      <c r="Y44" s="143"/>
     </row>
     <row r="45" spans="1:25" ht="15.75" thickBot="1">
       <c r="A45" s="7">
         <v>59</v>
       </c>
-      <c r="B45" s="146"/>
+      <c r="B45" s="155"/>
       <c r="C45" s="133" t="s">
+        <v>275</v>
+      </c>
+      <c r="D45" s="145" t="s">
         <v>276</v>
-      </c>
-      <c r="D45" s="152" t="s">
-        <v>277</v>
       </c>
       <c r="E45" s="112" t="s">
         <v>27</v>
       </c>
       <c r="F45" s="112" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G45" s="10" t="s">
         <v>160</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I45" s="28" t="s">
         <v>31</v>
@@ -6144,24 +6173,24 @@
       <c r="A46" s="7">
         <v>60</v>
       </c>
-      <c r="B46" s="146"/>
+      <c r="B46" s="155"/>
       <c r="C46" s="133" t="s">
+        <v>279</v>
+      </c>
+      <c r="D46" s="145" t="s">
         <v>280</v>
-      </c>
-      <c r="D46" s="152" t="s">
-        <v>281</v>
       </c>
       <c r="E46" s="112" t="s">
         <v>27</v>
       </c>
       <c r="F46" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="G46" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="G46" s="10" t="s">
+      <c r="H46" s="10" t="s">
         <v>283</v>
-      </c>
-      <c r="H46" s="10" t="s">
-        <v>284</v>
       </c>
       <c r="I46" s="28" t="s">
         <v>31</v>
@@ -6223,24 +6252,24 @@
       <c r="A47" s="7">
         <v>61</v>
       </c>
-      <c r="B47" s="146"/>
+      <c r="B47" s="155"/>
       <c r="C47" s="133" t="s">
+        <v>284</v>
+      </c>
+      <c r="D47" s="145" t="s">
         <v>285</v>
-      </c>
-      <c r="D47" s="152" t="s">
-        <v>286</v>
       </c>
       <c r="E47" s="112" t="s">
         <v>27</v>
       </c>
       <c r="F47" s="112" t="s">
+        <v>286</v>
+      </c>
+      <c r="G47" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="G47" s="10" t="s">
+      <c r="H47" s="10" t="s">
         <v>288</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>289</v>
       </c>
       <c r="I47" s="28" t="s">
         <v>31</v>
@@ -6302,24 +6331,24 @@
       <c r="A48" s="7">
         <v>62</v>
       </c>
-      <c r="B48" s="146"/>
+      <c r="B48" s="155"/>
       <c r="C48" s="133" t="s">
+        <v>289</v>
+      </c>
+      <c r="D48" s="145" t="s">
         <v>290</v>
-      </c>
-      <c r="D48" s="152" t="s">
-        <v>291</v>
       </c>
       <c r="E48" s="112" t="s">
         <v>27</v>
       </c>
       <c r="F48" s="112" t="s">
+        <v>291</v>
+      </c>
+      <c r="G48" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="G48" s="10" t="s">
+      <c r="H48" s="10" t="s">
         <v>293</v>
-      </c>
-      <c r="H48" s="10" t="s">
-        <v>294</v>
       </c>
       <c r="I48" s="28" t="s">
         <v>31</v>
@@ -6381,24 +6410,24 @@
       <c r="A49" s="7">
         <v>63</v>
       </c>
-      <c r="B49" s="146"/>
+      <c r="B49" s="155"/>
       <c r="C49" s="133" t="s">
+        <v>294</v>
+      </c>
+      <c r="D49" s="171" t="s">
         <v>295</v>
-      </c>
-      <c r="D49" s="163" t="s">
-        <v>296</v>
       </c>
       <c r="E49" s="112" t="s">
         <v>27</v>
       </c>
       <c r="F49" s="112" t="s">
+        <v>296</v>
+      </c>
+      <c r="G49" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="G49" s="10" t="s">
+      <c r="H49" s="10" t="s">
         <v>298</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>299</v>
       </c>
       <c r="I49" s="28" t="s">
         <v>31</v>
@@ -6460,24 +6489,24 @@
       <c r="A50" s="7">
         <v>64</v>
       </c>
-      <c r="B50" s="146"/>
+      <c r="B50" s="155"/>
       <c r="C50" s="133" t="s">
-        <v>295</v>
-      </c>
-      <c r="D50" s="163" t="s">
-        <v>300</v>
+        <v>294</v>
+      </c>
+      <c r="D50" s="171" t="s">
+        <v>299</v>
       </c>
       <c r="E50" s="112" t="s">
         <v>27</v>
       </c>
       <c r="F50" s="112" t="s">
+        <v>300</v>
+      </c>
+      <c r="G50" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="H50" s="10" t="s">
         <v>301</v>
-      </c>
-      <c r="G50" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="H50" s="10" t="s">
-        <v>302</v>
       </c>
       <c r="I50" s="28" t="s">
         <v>31</v>
@@ -6539,27 +6568,27 @@
       <c r="A51" s="7">
         <v>65</v>
       </c>
-      <c r="B51" s="146"/>
+      <c r="B51" s="155"/>
       <c r="C51" s="133" t="s">
+        <v>302</v>
+      </c>
+      <c r="D51" s="171" t="s">
         <v>303</v>
-      </c>
-      <c r="D51" s="163" t="s">
-        <v>304</v>
       </c>
       <c r="E51" s="112" t="s">
         <v>27</v>
       </c>
       <c r="F51" s="112" t="s">
+        <v>304</v>
+      </c>
+      <c r="G51" s="10" t="s">
         <v>305</v>
       </c>
-      <c r="G51" s="10" t="s">
+      <c r="H51" s="10" t="s">
         <v>306</v>
       </c>
-      <c r="H51" s="10" t="s">
+      <c r="I51" s="49" t="s">
         <v>307</v>
-      </c>
-      <c r="I51" s="49" t="s">
-        <v>308</v>
       </c>
       <c r="J51" s="41" t="s">
         <v>124</v>
@@ -6618,27 +6647,27 @@
       <c r="A52" s="7">
         <v>66</v>
       </c>
-      <c r="B52" s="146"/>
+      <c r="B52" s="155"/>
       <c r="C52" s="134" t="s">
+        <v>308</v>
+      </c>
+      <c r="D52" s="117" t="s">
         <v>309</v>
-      </c>
-      <c r="D52" s="117" t="s">
-        <v>310</v>
       </c>
       <c r="E52" s="117" t="s">
         <v>27</v>
       </c>
       <c r="F52" s="117" t="s">
+        <v>310</v>
+      </c>
+      <c r="G52" s="13" t="s">
         <v>311</v>
       </c>
-      <c r="G52" s="13" t="s">
+      <c r="H52" s="92" t="s">
         <v>312</v>
       </c>
-      <c r="H52" s="92" t="s">
-        <v>313</v>
-      </c>
       <c r="I52" s="96" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J52" s="92" t="s">
         <v>124</v>
@@ -6662,49 +6691,49 @@
       <c r="P52" s="97"/>
       <c r="Q52" s="97"/>
       <c r="R52" s="96" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="S52" s="96"/>
       <c r="T52" s="96" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="U52" s="96"/>
       <c r="V52" s="96" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="W52" s="96"/>
       <c r="X52" s="96" t="s">
+        <v>312</v>
+      </c>
+      <c r="Y52" s="106" t="s">
         <v>313</v>
-      </c>
-      <c r="Y52" s="106" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="53" spans="1:25">
       <c r="A53" s="7">
         <v>67</v>
       </c>
-      <c r="B53" s="146"/>
+      <c r="B53" s="155"/>
       <c r="C53" s="134" t="s">
+        <v>314</v>
+      </c>
+      <c r="D53" s="117" t="s">
         <v>315</v>
-      </c>
-      <c r="D53" s="117" t="s">
-        <v>316</v>
       </c>
       <c r="E53" s="117" t="s">
         <v>27</v>
       </c>
       <c r="F53" s="117" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G53" s="92" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H53" s="92" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I53" s="96" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J53" s="92" t="s">
         <v>124</v>
@@ -6728,49 +6757,49 @@
       <c r="P53" s="97"/>
       <c r="Q53" s="97"/>
       <c r="R53" s="96" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="S53" s="96"/>
       <c r="T53" s="96" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="U53" s="96"/>
       <c r="V53" s="96" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="W53" s="96"/>
       <c r="X53" s="96" t="s">
+        <v>312</v>
+      </c>
+      <c r="Y53" s="106" t="s">
         <v>313</v>
-      </c>
-      <c r="Y53" s="106" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="54" spans="1:25">
       <c r="A54" s="7">
         <v>68</v>
       </c>
-      <c r="B54" s="146"/>
+      <c r="B54" s="155"/>
       <c r="C54" s="134" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D54" s="117" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E54" s="117" t="s">
         <v>27</v>
       </c>
       <c r="F54" s="117" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G54" s="92" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H54" s="92" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I54" s="96" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J54" s="92" t="s">
         <v>124</v>
@@ -6794,49 +6823,49 @@
       <c r="P54" s="97"/>
       <c r="Q54" s="97"/>
       <c r="R54" s="96" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="S54" s="96"/>
       <c r="T54" s="96" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="U54" s="96"/>
       <c r="V54" s="96" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="W54" s="96"/>
       <c r="X54" s="96" t="s">
+        <v>312</v>
+      </c>
+      <c r="Y54" s="106" t="s">
         <v>313</v>
-      </c>
-      <c r="Y54" s="106" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="55" spans="1:25">
       <c r="A55" s="93">
         <v>69</v>
       </c>
-      <c r="B55" s="147"/>
+      <c r="B55" s="156"/>
       <c r="C55" s="135" t="s">
+        <v>319</v>
+      </c>
+      <c r="D55" s="136" t="s">
         <v>320</v>
-      </c>
-      <c r="D55" s="136" t="s">
-        <v>321</v>
       </c>
       <c r="E55" s="136" t="s">
         <v>27</v>
       </c>
       <c r="F55" s="136" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G55" s="94" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H55" s="94" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I55" s="98" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J55" s="94" t="s">
         <v>124</v>
@@ -6860,22 +6889,22 @@
       <c r="P55" s="100"/>
       <c r="Q55" s="100"/>
       <c r="R55" s="98" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="S55" s="98"/>
       <c r="T55" s="98" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="U55" s="98"/>
       <c r="V55" s="98" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="W55" s="98"/>
       <c r="X55" s="98" t="s">
+        <v>312</v>
+      </c>
+      <c r="Y55" s="107" t="s">
         <v>313</v>
-      </c>
-      <c r="Y55" s="107" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="56" spans="1:25">
@@ -6883,31 +6912,31 @@
         <v>70</v>
       </c>
       <c r="B56" s="22" t="s">
+        <v>322</v>
+      </c>
+      <c r="C56" s="137" t="s">
         <v>323</v>
       </c>
-      <c r="C56" s="137" t="s">
+      <c r="D56" s="138" t="s">
         <v>324</v>
-      </c>
-      <c r="D56" s="138" t="s">
-        <v>325</v>
       </c>
       <c r="E56" s="95" t="s">
         <v>27</v>
       </c>
       <c r="F56" s="95" t="s">
+        <v>325</v>
+      </c>
+      <c r="G56" s="95" t="s">
         <v>326</v>
       </c>
-      <c r="G56" s="95" t="s">
+      <c r="H56" s="138" t="s">
+        <v>324</v>
+      </c>
+      <c r="I56" s="138" t="s">
+        <v>324</v>
+      </c>
+      <c r="J56" s="138" t="s">
         <v>327</v>
-      </c>
-      <c r="H56" s="138" t="s">
-        <v>325</v>
-      </c>
-      <c r="I56" s="138" t="s">
-        <v>325</v>
-      </c>
-      <c r="J56" s="138" t="s">
-        <v>328</v>
       </c>
       <c r="K56" s="101">
         <v>1</v>
@@ -6925,16 +6954,16 @@
         <v>100</v>
       </c>
       <c r="O56" s="139" t="s">
+        <v>328</v>
+      </c>
+      <c r="P56" s="138" t="s">
+        <v>328</v>
+      </c>
+      <c r="Q56" s="139" t="s">
+        <v>328</v>
+      </c>
+      <c r="R56" s="102" t="s">
         <v>329</v>
-      </c>
-      <c r="P56" s="138" t="s">
-        <v>329</v>
-      </c>
-      <c r="Q56" s="139" t="s">
-        <v>329</v>
-      </c>
-      <c r="R56" s="102" t="s">
-        <v>330</v>
       </c>
       <c r="S56" s="103">
         <v>14</v>
@@ -6958,16 +6987,16 @@
         <v>1400</v>
       </c>
       <c r="Y56" s="108" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="57" spans="1:25" ht="18.75">
-      <c r="K57" s="143" t="s">
-        <v>332</v>
-      </c>
-      <c r="L57" s="143"/>
-      <c r="M57" s="143"/>
-      <c r="N57" s="143"/>
+      <c r="K57" s="152" t="s">
+        <v>331</v>
+      </c>
+      <c r="L57" s="152"/>
+      <c r="M57" s="152"/>
+      <c r="N57" s="152"/>
       <c r="T57" s="104">
         <f>SUM(T3:T56)</f>
         <v>279.48360000000002</v>
@@ -6982,12 +7011,12 @@
       </c>
     </row>
     <row r="58" spans="1:25" ht="18.75" customHeight="1">
-      <c r="K58" s="143" t="s">
-        <v>333</v>
-      </c>
-      <c r="L58" s="143"/>
-      <c r="M58" s="143"/>
-      <c r="N58" s="143"/>
+      <c r="K58" s="152" t="s">
+        <v>332</v>
+      </c>
+      <c r="L58" s="152"/>
+      <c r="M58" s="152"/>
+      <c r="N58" s="152"/>
       <c r="T58" s="104">
         <f>T57/5</f>
         <v>55.896720000000002</v>
@@ -7002,14 +7031,14 @@
       </c>
     </row>
     <row r="59" spans="1:25" ht="18.75">
-      <c r="K59" s="144" t="s">
+      <c r="K59" s="153" t="s">
+        <v>333</v>
+      </c>
+      <c r="L59" s="153"/>
+      <c r="M59" s="153"/>
+      <c r="N59" s="153"/>
+      <c r="S59" s="105" t="s">
         <v>334</v>
-      </c>
-      <c r="L59" s="144"/>
-      <c r="M59" s="144"/>
-      <c r="N59" s="144"/>
-      <c r="S59" s="105" t="s">
-        <v>335</v>
       </c>
       <c r="T59" s="55">
         <v>88</v>
@@ -7023,7 +7052,7 @@
     </row>
     <row r="60" spans="1:25">
       <c r="S60" s="105" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="T60" s="104">
         <f>SUM(T58:T59)</f>
@@ -7121,55 +7150,55 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="R3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="R4" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="R6" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="R7" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="R8" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="R11" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="R13" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="R14" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="R15" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="R16" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="R19" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="R21" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="R22" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="R23" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="R24" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="R25" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="R27" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="R29" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="R31" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="R33" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="R34" r:id="rId21" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="R36" r:id="rId22" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="R37" r:id="rId23" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="R38" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="R40" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="R42" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="R43" r:id="rId27" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="R45" r:id="rId28" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="R46" r:id="rId29" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="R47" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="R48" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="R49" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="R50" r:id="rId33" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="R9" r:id="rId34" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="R20" r:id="rId35" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="R12" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="R28" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="R30" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="R32" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="R35" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="R41" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="R51" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="R18" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="R26" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="R10" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="R5" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="R17" r:id="rId47" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="R56" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="R44" r:id="rId49" xr:uid="{523539CE-E9D2-4374-AD16-17B426F79A35}"/>
+    <hyperlink ref="R3" r:id="rId1"/>
+    <hyperlink ref="R4" r:id="rId2"/>
+    <hyperlink ref="R6" r:id="rId3"/>
+    <hyperlink ref="R7" r:id="rId4"/>
+    <hyperlink ref="R8" r:id="rId5"/>
+    <hyperlink ref="R11" r:id="rId6"/>
+    <hyperlink ref="R13" r:id="rId7"/>
+    <hyperlink ref="R14" r:id="rId8"/>
+    <hyperlink ref="R15" r:id="rId9"/>
+    <hyperlink ref="R16" r:id="rId10"/>
+    <hyperlink ref="R19" r:id="rId11"/>
+    <hyperlink ref="R21" r:id="rId12"/>
+    <hyperlink ref="R22" r:id="rId13"/>
+    <hyperlink ref="R23" r:id="rId14"/>
+    <hyperlink ref="R24" r:id="rId15"/>
+    <hyperlink ref="R25" r:id="rId16"/>
+    <hyperlink ref="R27" r:id="rId17"/>
+    <hyperlink ref="R29" r:id="rId18"/>
+    <hyperlink ref="R31" r:id="rId19"/>
+    <hyperlink ref="R33" r:id="rId20"/>
+    <hyperlink ref="R34" r:id="rId21"/>
+    <hyperlink ref="R36" r:id="rId22"/>
+    <hyperlink ref="R37" r:id="rId23"/>
+    <hyperlink ref="R38" r:id="rId24"/>
+    <hyperlink ref="R40" r:id="rId25"/>
+    <hyperlink ref="R42" r:id="rId26"/>
+    <hyperlink ref="R43" r:id="rId27"/>
+    <hyperlink ref="R45" r:id="rId28"/>
+    <hyperlink ref="R46" r:id="rId29"/>
+    <hyperlink ref="R47" r:id="rId30"/>
+    <hyperlink ref="R48" r:id="rId31"/>
+    <hyperlink ref="R49" r:id="rId32"/>
+    <hyperlink ref="R50" r:id="rId33"/>
+    <hyperlink ref="R9" r:id="rId34"/>
+    <hyperlink ref="R20" r:id="rId35"/>
+    <hyperlink ref="R12" r:id="rId36"/>
+    <hyperlink ref="R28" r:id="rId37"/>
+    <hyperlink ref="R30" r:id="rId38"/>
+    <hyperlink ref="R32" r:id="rId39"/>
+    <hyperlink ref="R35" r:id="rId40"/>
+    <hyperlink ref="R41" r:id="rId41"/>
+    <hyperlink ref="R51" r:id="rId42"/>
+    <hyperlink ref="R18" r:id="rId43"/>
+    <hyperlink ref="R26" r:id="rId44"/>
+    <hyperlink ref="R10" r:id="rId45"/>
+    <hyperlink ref="R5" r:id="rId46"/>
+    <hyperlink ref="R17" r:id="rId47"/>
+    <hyperlink ref="R56" r:id="rId48"/>
+    <hyperlink ref="R44" r:id="rId49"/>
   </hyperlinks>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.30555555555555602" right="0.30555555555555602" top="0.30555555555555602" bottom="0.30555555555555602" header="0" footer="0"/>
